--- a/new-info36/web.xlsx
+++ b/new-info36/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21585" windowHeight="10050"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="14" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
   <si>
     <t>domain</t>
   </si>
@@ -42,85 +42,85 @@
     <t>color2</t>
   </si>
   <si>
-    <t>play.radiciflorous.com</t>
+    <t>read.radiciflorous.com</t>
+  </si>
+  <si>
+    <t>#145f39</t>
+  </si>
+  <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>nimbiferous.com</t>
+  </si>
+  <si>
+    <t>#c4b091</t>
+  </si>
+  <si>
+    <t>daggledown.com</t>
+  </si>
+  <si>
+    <t>#fac03d</t>
+  </si>
+  <si>
+    <t>quodlibets.com</t>
+  </si>
+  <si>
+    <t>#aa9649</t>
+  </si>
+  <si>
+    <t>obganiate.com</t>
+  </si>
+  <si>
+    <t>#b65458</t>
+  </si>
+  <si>
+    <t>quagmiry.com</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>play.mettas.site</t>
+  </si>
+  <si>
+    <t>#957aa9</t>
+  </si>
+  <si>
+    <t>sec.mettas.site</t>
+  </si>
+  <si>
+    <t>#33325d</t>
+  </si>
+  <si>
+    <t>play.derives.cloud</t>
+  </si>
+  <si>
+    <t>#4189b3</t>
+  </si>
+  <si>
+    <t>sec.derives.cloud</t>
   </si>
   <si>
     <t>#ae1c31</t>
-  </si>
-  <si>
-    <t>sec.radiciflorous.com</t>
-  </si>
-  <si>
-    <t>#33325d</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>nimbiferous.com</t>
-  </si>
-  <si>
-    <t>#c4b091</t>
-  </si>
-  <si>
-    <t>daggledown.com</t>
-  </si>
-  <si>
-    <t>#fac03d</t>
-  </si>
-  <si>
-    <t>quodlibets.com</t>
-  </si>
-  <si>
-    <t>#aa9649</t>
-  </si>
-  <si>
-    <t>obganiate.com</t>
-  </si>
-  <si>
-    <t>#b65458</t>
-  </si>
-  <si>
-    <t>quagmiry.com</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
-  </si>
-  <si>
-    <t>play.mettas.site</t>
-  </si>
-  <si>
-    <t>#957aa9</t>
-  </si>
-  <si>
-    <t>sec.mettas.site</t>
-  </si>
-  <si>
-    <t>play.derives.cloud</t>
-  </si>
-  <si>
-    <t>#4189b3</t>
-  </si>
-  <si>
-    <t>sec.derives.cloud</t>
   </si>
   <si>
     <t>lagoonsea.com</t>
@@ -292,7 +292,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -424,6 +424,14 @@
     <font>
       <u/>
       <sz val="10"/>
+      <color rgb="FF175CEB"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
       <color rgb="FF1450B8"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -572,7 +580,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="58">
+  <fills count="59">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,6 +716,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF145F39"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1064,70 +1078,67 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1142,74 +1153,77 @@
     <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1320,28 +1334,25 @@
     <xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1759,18 +1770,14 @@
       <c r="C2" s="42"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="26"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="30"/>
@@ -1778,19 +1785,19 @@
       <c r="C6" s="30"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7">
+      <c r="F17" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="46" t="s">
+      <c r="G17" s="46" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7">
-      <c r="F17" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="47" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1798,8 +1805,7 @@
     <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
     <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
     <hyperlink ref="A6" r:id="rId3"/>
-    <hyperlink ref="A2" r:id="rId4" display="play.radiciflorous.com" tooltip="http://radiciflorous.com"/>
-    <hyperlink ref="A3" r:id="rId4" display="sec.radiciflorous.com" tooltip="http://radiciflorous.com"/>
+    <hyperlink ref="A2" r:id="rId4" display="read.radiciflorous.com" tooltip="http://radiciflorous.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1820,24 +1826,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2">
@@ -1849,10 +1855,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3">
@@ -1864,10 +1870,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4">
@@ -1879,10 +1885,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="35"/>
       <c r="D5">
@@ -1894,10 +1900,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="35"/>
       <c r="D6">
@@ -1943,24 +1949,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" s="28"/>
       <c r="D2">
@@ -1972,10 +1978,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3">
@@ -1987,10 +1993,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4">
@@ -2002,10 +2008,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="32" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>4</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5">
@@ -2048,16 +2054,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2352,7 +2358,7 @@
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" ht="15.75" spans="1:10">
+    <row r="12" spans="1:10">
       <c r="A12" s="14"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
